--- a/SAEN PEÑA/Mayo/SAENZ_EXPENSAS-MAYO.xlsx
+++ b/SAEN PEÑA/Mayo/SAENZ_EXPENSAS-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81D49BA-1246-401D-B119-0A097360FE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1BE130-B16D-4E28-8D21-DADD85CB72B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1236,6 +1236,7 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1293,7 +1294,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1737,10 +1737,10 @@
       <c r="B11" s="102"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="112" t="s">
+      <c r="E11" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="112"/>
+      <c r="F11" s="113"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="104" t="s">
@@ -1749,7 +1749,7 @@
       <c r="B12" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="131">
+      <c r="C12" s="112">
         <v>32362.99</v>
       </c>
       <c r="D12" s="5"/>
@@ -1786,8 +1786,8 @@
       <c r="B14" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="131">
-        <v>25249.58</v>
+      <c r="C14" s="112">
+        <v>25437.48</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="51" t="s">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="F14" s="52">
         <f>-(C34)</f>
-        <v>-205683.01</v>
+        <v>-205870.91</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1816,14 +1816,14 @@
       <c r="B16" s="108"/>
       <c r="C16" s="82">
         <f>SUM(C12:C15)</f>
-        <v>119659.57</v>
+        <v>119847.47</v>
       </c>
       <c r="E16" s="53" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="54">
         <f>SUM(F12:F15)</f>
-        <v>486172.49932840909</v>
+        <v>485984.59932840907</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1890,7 +1890,7 @@
       <c r="B22" s="41"/>
       <c r="C22" s="42">
         <f>+C21+C16</f>
-        <v>205683.01</v>
+        <v>205870.91</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C32" s="46">
         <f>C22-C20</f>
-        <v>205683.01</v>
+        <v>205870.91</v>
       </c>
       <c r="F32" s="6"/>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="C33" s="72">
         <f>+C22</f>
-        <v>205683.01</v>
+        <v>205870.91</v>
       </c>
       <c r="E33" s="105"/>
       <c r="F33" s="6"/>
@@ -1990,7 +1990,7 @@
       <c r="B34" s="58"/>
       <c r="C34" s="59">
         <f>C32</f>
-        <v>205683.01</v>
+        <v>205870.91</v>
       </c>
       <c r="E34" s="16"/>
     </row>
@@ -2502,18 +2502,18 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="113"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="113"/>
-      <c r="L12" s="113"/>
+      <c r="A12" s="114"/>
+      <c r="B12" s="114"/>
+      <c r="C12" s="114"/>
+      <c r="D12" s="114"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="114"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="114"/>
+      <c r="L12" s="114"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L13" s="6"/>
@@ -2541,60 +2541,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="122"/>
       <c r="F1" s="83"/>
       <c r="G1" s="83"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="123" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="125">
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="126">
         <v>565</v>
       </c>
-      <c r="E2" s="126"/>
+      <c r="E2" s="127"/>
       <c r="F2" s="84"/>
       <c r="G2" s="84"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="127" t="s">
+      <c r="A3" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="127" t="s">
+      <c r="C3" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="129" t="s">
+      <c r="D3" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="114" t="s">
+      <c r="E3" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="114" t="s">
+      <c r="F3" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="114" t="s">
+      <c r="G3" s="115" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="128"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="85">
@@ -2754,11 +2754,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="116"/>
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="118"/>
+      <c r="A12" s="117"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="119"/>
       <c r="F12" s="83"/>
       <c r="G12" s="83"/>
     </row>

--- a/SAEN PEÑA/Mayo/SAENZ_EXPENSAS-MAYO.xlsx
+++ b/SAEN PEÑA/Mayo/SAENZ_EXPENSAS-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1BE130-B16D-4E28-8D21-DADD85CB72B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05A3B39-9685-40FF-BFFA-07FDA4FBF0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
   <si>
     <t>UF</t>
   </si>
@@ -359,7 +359,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,6 +408,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1047,7 +1053,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1294,6 +1300,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1661,7 +1669,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1780,13 +1788,13 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="102" t="s">
+      <c r="A14" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="112">
+      <c r="C14" s="133">
         <v>25437.48</v>
       </c>
       <c r="D14" s="5"/>
@@ -1794,212 +1802,220 @@
         <v>22</v>
       </c>
       <c r="F14" s="52">
-        <f>-(C34)</f>
-        <v>-205870.91</v>
+        <f>-(C35)</f>
+        <v>-237412.49</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="102" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="75">
-        <v>32800</v>
-      </c>
+      <c r="A15" s="132" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="132"/>
+      <c r="C15" s="133">
+        <v>31541.58</v>
+      </c>
+      <c r="D15" s="5"/>
       <c r="E15" s="51"/>
       <c r="F15" s="52"/>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="107"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="82">
-        <f>SUM(C12:C15)</f>
-        <v>119847.47</v>
-      </c>
-      <c r="E16" s="53" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="75">
+        <v>32800</v>
+      </c>
+      <c r="E16" s="51"/>
+      <c r="F16" s="52"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="107"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="82">
+        <f>SUM(C12:C16)</f>
+        <v>151389.04999999999</v>
+      </c>
+      <c r="E17" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="54">
-        <f>SUM(F12:F15)</f>
-        <v>485984.59932840907</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="106" t="s">
+      <c r="F17" s="54">
+        <f>SUM(F12:F16)</f>
+        <v>454443.01932840911</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20"/>
-    </row>
-    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="110" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="75">
-        <f xml:space="preserve"> 51328.1</f>
-        <v>51328.1</v>
-      </c>
+      <c r="B18" s="102"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="102" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="110"/>
+        <v>42</v>
+      </c>
+      <c r="B19" s="110" t="s">
+        <v>71</v>
+      </c>
       <c r="C19" s="75">
-        <v>34695.339999999997</v>
+        <f xml:space="preserve"> 51328.1</f>
+        <v>51328.1</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="102"/>
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="102" t="s">
+        <v>69</v>
+      </c>
       <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
+      <c r="C20" s="75">
+        <v>34695.339999999997</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="107"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="82">
-        <f>SUM(C17:C20)</f>
+      <c r="A21" s="102"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="107"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="82">
+        <f>SUM(C18:C21)</f>
         <v>86023.44</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="42">
-        <f>+C21+C16</f>
-        <v>205870.91</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42">
+        <f>+C22+C17</f>
+        <v>237412.49</v>
+      </c>
+      <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="63" t="s">
         <v>27</v>
       </c>
+      <c r="B24" s="77"/>
+      <c r="C24" s="78"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="47"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="46">
-        <v>0</v>
-      </c>
+      <c r="A26" s="37"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="47"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
+      <c r="A27" s="45"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="46">
         <v>0</v>
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="73"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="76"/>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="55"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="46">
+        <v>0</v>
+      </c>
       <c r="F28" s="6"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="73"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="81"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="76"/>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="73"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="76">
-        <v>0</v>
-      </c>
+      <c r="B30" s="80"/>
+      <c r="C30" s="81"/>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="73"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="76">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="58"/>
-      <c r="C31" s="59">
-        <f>SUM(C26:C30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" s="58"/>
+      <c r="C32" s="59">
+        <f>SUM(C27:C31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="46">
-        <f>C22-C20</f>
-        <v>205870.91</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="C33" s="46">
+        <f>C23-C21</f>
+        <v>237412.49</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="72">
-        <f>+C22</f>
-        <v>205870.91</v>
-      </c>
-      <c r="E33" s="105"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+      <c r="C34" s="72">
+        <f>+C23</f>
+        <v>237412.49</v>
+      </c>
+      <c r="E34" s="105"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="59">
-        <f>C32</f>
-        <v>205870.91</v>
-      </c>
-      <c r="E34" s="16"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D39" s="6"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="59">
+        <f>C33</f>
+        <v>237412.49</v>
+      </c>
+      <c r="E35" s="16"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="D40" s="6"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D41" s="16"/>
@@ -2007,19 +2023,18 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D43" s="16"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="20"/>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D44" s="16"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="18"/>
+      <c r="A56" s="19"/>
       <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
+      <c r="C56" s="20"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="18"/>
@@ -2050,6 +2065,11 @@
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SAEN PEÑA/Mayo/SAENZ_EXPENSAS-MAYO.xlsx
+++ b/SAEN PEÑA/Mayo/SAENZ_EXPENSAS-MAYO.xlsx
@@ -5,24 +5,27 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05A3B39-9685-40FF-BFFA-07FDA4FBF0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AD99D6-732F-4628-AF61-FAF3C2C29E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$35</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="74">
   <si>
     <t>UF</t>
   </si>
@@ -231,13 +234,19 @@
     <t>Honorarios</t>
   </si>
   <si>
-    <t>Distribuidora Barbiero -  compra de automatico</t>
-  </si>
-  <si>
     <t>Liquidacion mes de MAYO</t>
   </si>
   <si>
     <t xml:space="preserve">Período MAYO </t>
+  </si>
+  <si>
+    <t>EL EDESUR DE JUNIO LO PAGAMOS SIN QUERES EN MAYO -  ES DE 31541,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra de picaporte </t>
+  </si>
+  <si>
+    <t>Prevision</t>
   </si>
 </sst>
 </file>
@@ -250,7 +259,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,13 +360,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1053,7 +1055,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1242,7 +1244,6 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1300,8 +1301,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1669,23 +1669,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1693,27 +1693,27 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1721,11 +1721,11 @@
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
       <c r="E7" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="103"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1733,31 +1733,31 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="106" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="102"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="113" t="s">
+      <c r="E11" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="113"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="112"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="104" t="s">
         <v>61</v>
       </c>
       <c r="B12" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="112">
+      <c r="C12" s="111">
         <v>32362.99</v>
       </c>
       <c r="D12" s="5"/>
@@ -1765,10 +1765,10 @@
         <v>48</v>
       </c>
       <c r="F12" s="50">
-        <v>398111.03351840901</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>487962.0693284091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="102" t="s">
         <v>66</v>
       </c>
@@ -1784,17 +1784,17 @@
       </c>
       <c r="F13" s="52">
         <f>'prorrateo '!F11</f>
-        <v>293744.47581000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="132" t="s">
+        <v>135915.367104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="132" t="s">
+      <c r="B14" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="133">
+      <c r="C14" s="111">
         <v>25437.48</v>
       </c>
       <c r="D14" s="5"/>
@@ -1802,274 +1802,267 @@
         <v>22</v>
       </c>
       <c r="F14" s="52">
-        <f>-(C35)</f>
-        <v>-237412.49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="132" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="132"/>
-      <c r="C15" s="133">
-        <v>31541.58</v>
-      </c>
-      <c r="D15" s="5"/>
+        <f>-(C34)</f>
+        <v>-186802.05499999999</v>
+      </c>
+      <c r="G14" s="131" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="75">
+        <v>32800</v>
+      </c>
       <c r="E15" s="51"/>
       <c r="F15" s="52"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="102" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="75">
-        <v>32800</v>
-      </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="52"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="107"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="82">
-        <f>SUM(C12:C16)</f>
-        <v>151389.04999999999</v>
-      </c>
-      <c r="E17" s="53" t="s">
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="107"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="82">
+        <f>SUM(C12:C15)</f>
+        <v>119847.47</v>
+      </c>
+      <c r="E16" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="54">
-        <f>SUM(F12:F16)</f>
-        <v>454443.01932840911</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="106" t="s">
+      <c r="F16" s="54">
+        <f>SUM(F12:F15)</f>
+        <v>437075.38143240911</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="102"/>
-      <c r="C18" s="109"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="75">
+        <f xml:space="preserve"> 51328.1+51328.1*5%</f>
+        <v>53894.504999999997</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="110" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="75">
-        <f xml:space="preserve"> 51328.1</f>
-        <v>51328.1</v>
+        <v>72</v>
+      </c>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111">
+        <v>13060.08</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="102" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B20" s="110"/>
-      <c r="C20" s="75">
-        <v>34695.339999999997</v>
-      </c>
+      <c r="C20" s="111"/>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="102"/>
-      <c r="B21" s="110"/>
-      <c r="C21" s="111"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="107"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="82">
+        <f>SUM(C17:C20)</f>
+        <v>66954.584999999992</v>
+      </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="107"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="82">
-        <f>SUM(C18:C21)</f>
-        <v>86023.44</v>
+      <c r="E21" s="5"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42">
+        <f>+C21+C16</f>
+        <v>186802.05499999999</v>
       </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="42">
-        <f>+C22+C17</f>
-        <v>237412.49</v>
-      </c>
-      <c r="D23" s="5"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="77"/>
+      <c r="C23" s="78"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="63" t="s">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="77"/>
-      <c r="C24" s="78"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="47"/>
+    </row>
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="37"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="47"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="45"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="46">
+        <v>0</v>
+      </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
-      <c r="B27" s="44"/>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
       <c r="C27" s="46">
         <v>0</v>
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="55"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="46">
-        <v>0</v>
-      </c>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="73"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="76"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="73"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="76"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="81"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="73"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="81"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="76">
+        <v>0</v>
+      </c>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="76">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="57" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="59">
-        <f>SUM(C27:C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B31" s="58"/>
+      <c r="C31" s="59">
+        <f>SUM(C26:C30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="46">
-        <f>C23-C21</f>
-        <v>237412.49</v>
-      </c>
+      <c r="C32" s="46">
+        <f>C22-C20</f>
+        <v>186802.05499999999</v>
+      </c>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="72">
+        <f>+C22</f>
+        <v>186802.05499999999</v>
+      </c>
+      <c r="E33" s="105"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="72">
-        <f>+C23</f>
-        <v>237412.49</v>
-      </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="57" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="59">
-        <f>C33</f>
-        <v>237412.49</v>
-      </c>
-      <c r="E35" s="16"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="58"/>
+      <c r="C34" s="59">
+        <f>C32</f>
+        <v>186802.05499999999</v>
+      </c>
+      <c r="E34" s="16"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D44" s="16"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="19"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="19"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="20"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="18"/>
       <c r="B56" s="18"/>
-      <c r="C56" s="20"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="18"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2091,24 +2084,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="100" t="s">
         <v>60</v>
       </c>
@@ -2126,11 +2119,11 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="65">
-        <v>203893.44</v>
+        <v>186802.05499999999</v>
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
@@ -2149,7 +2142,7 @@
       <c r="K2" s="70"/>
       <c r="L2" s="71"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2187,7 +2180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2217,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2231,11 +2224,11 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>53933.411952000002</v>
+        <v>30828.688128000002</v>
       </c>
       <c r="F5" s="75">
         <f t="shared" ref="F5:F8" si="0">E5</f>
-        <v>53933.411952000002</v>
+        <v>30828.688128000002</v>
       </c>
       <c r="G5" s="61">
         <f>E5-F5</f>
@@ -2250,7 +2243,7 @@
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>30828.688128000002</v>
+        <v>28244.470716</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2258,10 +2251,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>30828.688128000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>28244.470716</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2275,26 +2268,23 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>55966.615974000008</v>
-      </c>
-      <c r="F6" s="75">
-        <f>E6</f>
-        <v>55966.615974000008</v>
-      </c>
+        <v>31990.880736000003</v>
+      </c>
+      <c r="F6" s="75"/>
       <c r="G6" s="61">
         <f t="shared" ref="G6:G8" si="1">E6-F6</f>
-        <v>0</v>
+        <v>31990.880736000003</v>
       </c>
       <c r="H6" s="64">
         <f t="shared" ref="H6:H10" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>0</v>
+        <v>2687.2339818240002</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>31990.880736000003</v>
+        <v>29309.242429500002</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2302,10 +2292,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>31990.880736000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>63987.357147324001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2319,11 +2309,11 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>56430.329172000005</v>
+        <v>32255.942208</v>
       </c>
       <c r="F7" s="75">
         <f t="shared" si="0"/>
-        <v>56430.329172000005</v>
+        <v>32255.942208</v>
       </c>
       <c r="G7" s="61">
         <f t="shared" si="1"/>
@@ -2338,7 +2328,7 @@
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>32255.942208</v>
+        <v>29552.085101000001</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2346,10 +2336,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>32255.942208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>29552.085101000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2363,11 +2353,11 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>70627.087080000012</v>
+        <v>40370.901120000002</v>
       </c>
       <c r="F8" s="75">
         <f t="shared" si="0"/>
-        <v>70627.087080000012</v>
+        <v>40370.901120000002</v>
       </c>
       <c r="G8" s="61">
         <f t="shared" si="1"/>
@@ -2382,7 +2372,7 @@
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>40370.901120000002</v>
+        <v>36986.80689</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2390,10 +2380,10 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="3"/>
-        <v>40370.901120000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>36986.80689</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2407,11 +2397,11 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>56787.031632000006</v>
+        <v>32459.835648</v>
       </c>
       <c r="F9" s="75">
         <f>E9</f>
-        <v>56787.031632000006</v>
+        <v>32459.835648</v>
       </c>
       <c r="G9" s="61">
         <f>E9-F9</f>
@@ -2426,7 +2416,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>32459.835648</v>
+        <v>29738.887156000001</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2434,10 +2424,10 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="3"/>
-        <v>32459.835648</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>29738.887156000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2451,23 +2441,23 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>62957.984190000003</v>
+        <v>104233.64702196</v>
       </c>
       <c r="F10" s="75"/>
       <c r="G10" s="61">
         <f>E10-F10</f>
-        <v>62957.984190000003</v>
+        <v>104233.64702196</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="2"/>
-        <v>5288.4706719600008</v>
+        <v>8755.6263498446406</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>35987.192159999999</v>
+        <v>32970.562707499994</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2475,10 +2465,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>104233.64702196</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>145959.83607930463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2490,19 +2480,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>356702.46</v>
+        <v>272139.89486195997</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>293744.47581000003</v>
+        <v>135915.367104</v>
       </c>
       <c r="G11" s="43">
         <f>SUM(G5:G10)</f>
-        <v>62957.984190000003</v>
+        <v>136224.52775795999</v>
       </c>
       <c r="H11" s="43">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>5288.4706719600008</v>
+        <v>11442.86033166864</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2510,7 +2500,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="5"/>
-        <v>203893.44</v>
+        <v>186802.05499999999</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="5"/>
@@ -2518,27 +2508,27 @@
       </c>
       <c r="L11" s="43">
         <f>SUM(L5:L10)</f>
-        <v>272139.89486195997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="114"/>
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="114"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>334469.44308962865</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="113"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2555,68 +2545,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="122"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="121"/>
       <c r="F1" s="83"/>
       <c r="G1" s="83"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="123" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126">
+      <c r="B2" s="123"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="125">
         <v>565</v>
       </c>
-      <c r="E2" s="127"/>
+      <c r="E2" s="126"/>
       <c r="F2" s="84"/>
       <c r="G2" s="84"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="128" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="128" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="115" t="s">
+      <c r="E3" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="115" t="s">
+      <c r="F3" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="115" t="s">
+      <c r="G3" s="114" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="129"/>
-      <c r="B4" s="129"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="128"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="85">
         <v>1</v>
       </c>
@@ -2639,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="85">
         <v>2</v>
       </c>
@@ -2662,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="85">
         <v>3</v>
       </c>
@@ -2685,7 +2675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="85">
         <v>4</v>
       </c>
@@ -2708,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85">
         <v>5</v>
       </c>
@@ -2731,7 +2721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="90">
         <v>6</v>
       </c>
@@ -2754,7 +2744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="95" t="s">
         <v>10</v>
       </c>
@@ -2773,12 +2763,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="117"/>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="119"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="116"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="118"/>
       <c r="F12" s="83"/>
       <c r="G12" s="83"/>
     </row>
